--- a/graphs/practica_IIIb/datos_isotermas.xlsx
+++ b/graphs/practica_IIIb/datos_isotermas.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Miguel\UAB\TERCER\LAB Termo\Repositori\graphs\practica_IIIb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910CE4D8-5ADC-4C8A-B61D-82172BB85396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704AABAE-67F7-4D2F-9723-8D9967CC629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Semana 2" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos Semana 2'!$D$34:$F$58</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="40">
   <si>
     <t>Presión sistema (bar)</t>
   </si>
@@ -112,6 +116,48 @@
   <si>
     <t>T = 30,3°C</t>
   </si>
+  <si>
+    <t>copia de seguridad</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+  </si>
+  <si>
+    <t>Cherry picking 1 cambios y quitar</t>
+  </si>
+  <si>
+    <t>1) Igualar a la presión de vapor</t>
+  </si>
+  <si>
+    <t>2) El volumen de los extremos será la media de el punto de transición</t>
+  </si>
+  <si>
+    <t>3) Movemos los puntos de 45</t>
+  </si>
+  <si>
+    <t>4) El de 20 &gt; lo movemos uno a la derecha</t>
+  </si>
+  <si>
+    <t>incertidumbres V</t>
+  </si>
+  <si>
+    <t>delta V</t>
+  </si>
+  <si>
+    <t>p_vap</t>
+  </si>
+  <si>
+    <t>prod</t>
+  </si>
+  <si>
+    <t>ln T</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
 </sst>
 </file>
 
@@ -142,7 +188,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,8 +213,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -290,11 +342,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -317,11 +378,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -344,19 +413,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -939,7 +1007,2097 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="9.7112860892388452E-5"/>
+                  <c:y val="-0.10226851851851852"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$AG$2:$AG$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$AH$2:$AH$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6039-4600-A0FF-3D2ADB062220}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1318471760"/>
+        <c:axId val="1318478000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1318471760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1318478000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1318478000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1318471760"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.2692038495188102E-2"/>
+          <c:y val="0.19486111111111112"/>
+          <c:w val="0.88707874015748034"/>
+          <c:h val="0.72088764946048411"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>prueba 2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.7180664916885389E-3"/>
+                  <c:y val="-0.15319444444444444"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$AG$2:$AG$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$Q$65:$Q$72</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BBBA-494F-AA58-A7D4C3D3E390}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="425627056"/>
+        <c:axId val="425626576"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="425627056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="425626576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="425626576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="425627056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Datos Semana 2'!$P$65:$P$72</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1,5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1,1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1,025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0,9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0,725</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0,5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0,4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0,1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.58177274715660543"/>
+                  <c:y val="2.3674540682414782E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$P$65:$P$72</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90000000000000013</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.72500000000000009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39999999999999991</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.9999999999999978E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$AG$2:$AG$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E4FA-459D-9821-247A0B1CEFCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1273114656"/>
+        <c:axId val="1273111776"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1273114656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273111776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1273111776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273114656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>con el log</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$S$65:$S$72</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.0374264979406236</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1958996524092338</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3053513694466237</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.403120521175818</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.481442628502305</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5440680443502757</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6020599913279623</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6503075231319364</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$Q$65:$Q$72</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0B3B-49FF-9056-A6A84B72483B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="429700608"/>
+        <c:axId val="1273115136"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="429700608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273115136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1273115136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="429700608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>con la inversa</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$O$76:$O$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.6666666666666666E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.3333333333333333E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.8571428571428571E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2222222222222223E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Datos Semana 2'!$Q$65:$Q$72</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5623-465F-BF64-A6226DF3DEB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1269511200"/>
+        <c:axId val="1269510720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1269511200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1269510720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1269510720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1269511200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1495,20 +3653,2600 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>68852</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>541019</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19322</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>428624</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>96338</xdr:rowOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>220979</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>73478</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1528,6 +6266,186 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>44767</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>132397</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>349567</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>155257</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9CE736B-D6D1-8957-8C96-A853338850B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{470EC538-6FE7-97CB-B804-00D80C249F99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>942975</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A8B73BE-0436-D862-2501-817689A0C540}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F61C622-F178-C0B9-6168-6AC0FFAA2414}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE3A1053-AA8C-2473-F06C-443DBC6BBDBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1823,28 +6741,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:AE80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:AI87"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="4" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="7" width="5.77734375" customWidth="1"/>
-    <col min="8" max="10" width="14.77734375" customWidth="1"/>
-    <col min="11" max="11" width="5.77734375" customWidth="1"/>
-    <col min="12" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="15" width="5.77734375" customWidth="1"/>
-    <col min="16" max="18" width="14.77734375" customWidth="1"/>
-    <col min="19" max="20" width="5.77734375" customWidth="1"/>
-    <col min="21" max="22" width="14.77734375" customWidth="1"/>
-    <col min="23" max="23" width="5.77734375" customWidth="1"/>
-    <col min="24" max="25" width="14.77734375" customWidth="1"/>
-    <col min="26" max="26" width="5.77734375" customWidth="1"/>
-    <col min="27" max="28" width="14.77734375" customWidth="1"/>
-    <col min="29" max="29" width="5.77734375" customWidth="1"/>
-    <col min="30" max="31" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="4" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" customWidth="1"/>
+    <col min="16" max="18" width="14.7109375" customWidth="1"/>
+    <col min="19" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" customWidth="1"/>
+    <col min="23" max="23" width="5.7109375" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" customWidth="1"/>
+    <col min="26" max="26" width="5.7109375" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" customWidth="1"/>
+    <col min="29" max="29" width="5.7109375" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="H1">
         <v>8</v>
       </c>
@@ -1863,130 +6781,160 @@
       <c r="P1">
         <v>16</v>
       </c>
+      <c r="AE1">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="D2" s="21" t="s">
+    <row r="2" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="D2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="H2" s="21" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="H2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="L2" s="21" t="s">
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="L2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="P2" s="21" t="s">
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="P2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="U2" s="13" t="s">
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="U2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="13"/>
-      <c r="X2" s="13" t="s">
+      <c r="V2" s="28"/>
+      <c r="X2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="13"/>
-      <c r="AA2" s="13" t="s">
+      <c r="Y2" s="28"/>
+      <c r="AA2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="13"/>
-      <c r="AD2" s="13" t="s">
+      <c r="AB2" s="28"/>
+      <c r="AD2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="AE2" s="13"/>
+      <c r="AE2" s="28"/>
+      <c r="AG2">
+        <v>10.9</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="3" spans="2:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="24" t="s">
+    <row r="3" spans="2:35" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="V3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="X3" s="12" t="s">
+      <c r="X3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Y3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="12" t="s">
+      <c r="AA3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" s="12" t="s">
+      <c r="AB3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="AD3" s="12" t="s">
+      <c r="AD3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AE3" s="12" t="s">
+      <c r="AE3" s="27" t="s">
         <v>24</v>
       </c>
+      <c r="AG3">
+        <v>15.7</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12"/>
+    <row r="4" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AG4">
+        <v>20.2</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>23</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2058,8 +7006,17 @@
         <f>1/Q5</f>
         <v>0.25</v>
       </c>
+      <c r="AG5">
+        <v>25.3</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>25.5</v>
+      </c>
+      <c r="AI5" s="5">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2131,8 +7088,17 @@
         <f t="shared" ref="AE6:AE24" si="6">1/Q6</f>
         <v>0.26315789473684209</v>
       </c>
+      <c r="AG6">
+        <v>30.3</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>28</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="7" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D7" s="1">
         <v>10.5</v>
       </c>
@@ -2201,8 +7167,17 @@
         <f t="shared" si="6"/>
         <v>0.27777777777777779</v>
       </c>
+      <c r="AG7">
+        <v>35</v>
+      </c>
+      <c r="AH7" s="9">
+        <v>35.5</v>
+      </c>
+      <c r="AI7" s="9">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
@@ -2274,9 +7249,20 @@
         <f t="shared" si="6"/>
         <v>0.29411764705882354</v>
       </c>
+      <c r="AG8">
+        <v>40</v>
+      </c>
+      <c r="AH8" s="5">
+        <v>38.5</v>
+      </c>
+      <c r="AI8" s="5">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B9" s="11"/>
+    <row r="9" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B9" s="11">
+        <v>0.2</v>
+      </c>
       <c r="D9" s="1">
         <v>11.5</v>
       </c>
@@ -2304,8 +7290,8 @@
       <c r="N9" s="1">
         <v>3.2</v>
       </c>
-      <c r="P9" s="1">
-        <v>11.5</v>
+      <c r="P9" s="13">
+        <v>12.5</v>
       </c>
       <c r="Q9" s="1">
         <v>3.2</v>
@@ -2339,14 +7325,23 @@
       </c>
       <c r="AD9" s="1">
         <f t="shared" si="5"/>
-        <v>36.800000000000004</v>
+        <v>40</v>
       </c>
       <c r="AE9" s="1">
         <f t="shared" si="6"/>
         <v>0.3125</v>
       </c>
+      <c r="AG9">
+        <v>44.7</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>42</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D10" s="1">
         <v>12</v>
       </c>
@@ -2416,7 +7411,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>18</v>
       </c>
@@ -2489,7 +7484,7 @@
         <v>0.35714285714285715</v>
       </c>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
       <c r="D12" s="2">
         <v>13.5</v>
@@ -2560,7 +7555,7 @@
         <v>0.38461538461538458</v>
       </c>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D13" s="1">
         <v>14.5</v>
       </c>
@@ -2630,7 +7625,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>19</v>
       </c>
@@ -2703,8 +7698,10 @@
         <v>0.45454545454545453</v>
       </c>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B15" s="11"/>
+    <row r="15" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B15" s="11">
+        <v>0.2</v>
+      </c>
       <c r="D15" s="1">
         <v>16.5</v>
       </c>
@@ -2774,7 +7771,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:35" x14ac:dyDescent="0.25">
       <c r="D16" s="1">
         <v>18</v>
       </c>
@@ -2844,7 +7841,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="17" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D17" s="1">
         <v>19.5</v>
       </c>
@@ -2914,7 +7911,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="18" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <v>21.5</v>
       </c>
@@ -2984,7 +7981,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="19" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D19" s="1">
         <v>23</v>
       </c>
@@ -3054,7 +8051,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="20" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D20" s="6">
         <v>24</v>
       </c>
@@ -3124,7 +8121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D21" s="1">
         <v>24</v>
       </c>
@@ -3194,7 +8191,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="22" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D22" s="1">
         <v>24</v>
       </c>
@@ -3264,7 +8261,7 @@
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="23" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D23" s="1">
         <v>24.5</v>
       </c>
@@ -3334,7 +8331,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="24" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D24" s="1">
         <v>24.5</v>
       </c>
@@ -3404,7 +8401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D25" s="1">
         <v>24.6</v>
       </c>
@@ -3432,11 +8429,11 @@
       <c r="N25" s="5">
         <v>0</v>
       </c>
-      <c r="P25" s="14" t="s">
+      <c r="P25" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="16"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="20"/>
       <c r="U25" s="1">
         <f t="shared" si="0"/>
         <v>6.15</v>
@@ -3462,7 +8459,7 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="26" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D26" s="5">
         <v>25.5</v>
       </c>
@@ -3481,14 +8478,14 @@
       <c r="J26" s="5">
         <v>0</v>
       </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="20"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="23"/>
       <c r="U26" s="1">
         <f t="shared" si="0"/>
         <v>5.1000000000000005</v>
@@ -3506,7 +8503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D27" s="7">
         <v>35</v>
       </c>
@@ -3525,9 +8522,9 @@
       <c r="J27" s="1">
         <v>0</v>
       </c>
-      <c r="L27" s="17"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="19"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="23"/>
       <c r="U27" s="1">
         <f t="shared" si="0"/>
         <v>5.25</v>
@@ -3545,162 +8542,159 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D28" s="14" t="s">
+    <row r="28" spans="4:31" x14ac:dyDescent="0.25">
+      <c r="D28" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
-      <c r="H28" s="14" t="s">
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="H28" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="16"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="17"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="19"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="19"/>
+    <row r="29" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="23"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:31" x14ac:dyDescent="0.25">
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
-      <c r="U30">
-        <v>1</v>
-      </c>
-      <c r="W30" s="25"/>
+      <c r="W30" s="12"/>
     </row>
-    <row r="31" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="34" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D34" s="21" t="s">
+    <row r="34" spans="4:31" x14ac:dyDescent="0.25">
+      <c r="D34" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="H34" s="21" t="s">
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="H34" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="L34" s="21" t="s">
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="L34" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-      <c r="P34" s="21" t="s">
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="P34" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-      <c r="U34" s="13" t="s">
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="U34" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="V34" s="13"/>
-      <c r="X34" s="13" t="s">
+      <c r="V34" s="28"/>
+      <c r="X34" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="Y34" s="13"/>
-      <c r="AA34" s="13" t="s">
+      <c r="Y34" s="28"/>
+      <c r="AA34" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="AB34" s="13"/>
-      <c r="AD34" s="13" t="s">
+      <c r="AB34" s="28"/>
+      <c r="AD34" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="AE34" s="13"/>
+      <c r="AE34" s="28"/>
     </row>
-    <row r="35" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D35" s="22" t="s">
+    <row r="35" spans="4:31" x14ac:dyDescent="0.25">
+      <c r="D35" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="I35" s="22" t="s">
+      <c r="I35" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="J35" s="22" t="s">
+      <c r="J35" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L35" s="22" t="s">
+      <c r="L35" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="M35" s="22" t="s">
+      <c r="M35" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="N35" s="22" t="s">
+      <c r="N35" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="P35" s="22" t="s">
+      <c r="P35" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="Q35" s="22" t="s">
+      <c r="Q35" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="R35" s="22" t="s">
+      <c r="R35" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="U35" s="12" t="s">
+      <c r="U35" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="V35" s="12" t="s">
+      <c r="V35" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="X35" s="12" t="s">
+      <c r="X35" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="Y35" s="12" t="s">
+      <c r="Y35" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="AA35" s="12" t="s">
+      <c r="AA35" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AB35" s="12" t="s">
+      <c r="AB35" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="AD35" s="12" t="s">
+      <c r="AD35" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AE35" s="12" t="s">
+      <c r="AE35" s="27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="AA36" s="12"/>
-      <c r="AB36" s="12"/>
-      <c r="AD36" s="12"/>
-      <c r="AE36" s="12"/>
+    <row r="36" spans="4:31" x14ac:dyDescent="0.25">
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="U36" s="27"/>
+      <c r="V36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
+      <c r="AA36" s="27"/>
+      <c r="AB36" s="27"/>
+      <c r="AD36" s="27"/>
+      <c r="AE36" s="27"/>
     </row>
-    <row r="37" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D37" s="1">
         <v>9.5</v>
       </c>
@@ -3770,7 +8764,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="38" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D38" s="1">
         <v>10</v>
       </c>
@@ -3840,7 +8834,7 @@
         <v>0.26315789473684209</v>
       </c>
     </row>
-    <row r="39" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D39" s="1">
         <v>10.5</v>
       </c>
@@ -3910,7 +8904,7 @@
         <v>0.27777777777777779</v>
       </c>
     </row>
-    <row r="40" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D40" s="1">
         <v>11</v>
       </c>
@@ -3980,7 +8974,7 @@
         <v>0.29411764705882354</v>
       </c>
     </row>
-    <row r="41" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D41" s="1">
         <v>11.5</v>
       </c>
@@ -4050,7 +9044,7 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="42" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D42" s="1">
         <v>12</v>
       </c>
@@ -4120,7 +9114,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="43" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D43" s="1">
         <v>12.5</v>
       </c>
@@ -4190,7 +9184,7 @@
         <v>0.35714285714285715</v>
       </c>
     </row>
-    <row r="44" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D44" s="1">
         <v>13.5</v>
       </c>
@@ -4260,7 +9254,7 @@
         <v>0.38461538461538458</v>
       </c>
     </row>
-    <row r="45" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D45" s="1">
         <v>14</v>
       </c>
@@ -4330,7 +9324,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="46" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D46" s="1">
         <v>15</v>
       </c>
@@ -4400,7 +9394,7 @@
         <v>0.45454545454545453</v>
       </c>
     </row>
-    <row r="47" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D47" s="1">
         <v>16</v>
       </c>
@@ -4470,7 +9464,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:31" x14ac:dyDescent="0.25">
       <c r="D48" s="1">
         <v>17.5</v>
       </c>
@@ -4540,7 +9534,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="49" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D49" s="1">
         <v>18.5</v>
       </c>
@@ -4610,7 +9604,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="50" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D50" s="6">
         <v>19.5</v>
       </c>
@@ -4680,7 +9674,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="51" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D51" s="1">
         <v>19.5</v>
       </c>
@@ -4750,7 +9744,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="52" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D52" s="1">
         <v>19.5</v>
       </c>
@@ -4820,7 +9814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D53" s="1">
         <v>19.5</v>
       </c>
@@ -4890,7 +9884,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="54" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D54" s="1">
         <v>19.5</v>
       </c>
@@ -4960,7 +9954,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="55" spans="4:31" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:31" x14ac:dyDescent="0.25">
       <c r="D55" s="1">
         <v>19.5</v>
       </c>
@@ -5030,7 +10024,7 @@
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="56" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D56" s="9">
         <v>24.5</v>
       </c>
@@ -5100,17 +10094,17 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="57" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D57" s="14" t="s">
+    <row r="57" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="D57" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="16"/>
-      <c r="H57" s="14" t="s">
+      <c r="E57" s="19"/>
+      <c r="F57" s="20"/>
+      <c r="H57" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="16"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="20"/>
       <c r="L57" s="1">
         <v>18.5</v>
       </c>
@@ -5146,13 +10140,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D58" s="17"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="19"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="19"/>
+    <row r="58" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D58" s="21"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="23"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="23"/>
       <c r="L58" s="9">
         <v>21</v>
       </c>
@@ -5188,170 +10182,744 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="59" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="L59" s="14" t="s">
+    <row r="59" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="L59" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="M59" s="15"/>
-      <c r="N59" s="16"/>
-      <c r="P59" s="14" t="s">
+      <c r="M59" s="19"/>
+      <c r="N59" s="20"/>
+      <c r="P59" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="Q59" s="15"/>
-      <c r="R59" s="16"/>
+      <c r="Q59" s="19"/>
+      <c r="R59" s="20"/>
     </row>
-    <row r="60" spans="4:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L60" s="17"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="19"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="18"/>
-      <c r="R60" s="19"/>
+    <row r="60" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L60" s="21"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="23"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="22"/>
+      <c r="R60" s="23"/>
     </row>
-    <row r="63" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D63" s="20" t="s">
+    <row r="63" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="D63" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E63" s="20"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" s="25"/>
+      <c r="L63" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="M63" s="26"/>
     </row>
-    <row r="64" spans="4:31" x14ac:dyDescent="0.3">
-      <c r="D64" s="6">
+    <row r="64" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="B64" s="26">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64">
         <v>24</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64">
+        <f>AVERAGE(E19:E20)</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F64">
+        <f>E19 - E20</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H64" s="6">
+        <v>24</v>
+      </c>
+      <c r="I64" s="6">
         <v>1</v>
       </c>
+      <c r="L64">
+        <v>24</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>39</v>
+      </c>
+      <c r="P64" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>36</v>
+      </c>
+      <c r="R64" t="s">
+        <v>37</v>
+      </c>
+      <c r="S64" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D65" s="5">
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B65" s="26"/>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65">
+        <v>24</v>
+      </c>
+      <c r="E65">
+        <v>0.2</v>
+      </c>
+      <c r="H65" s="5">
         <v>25.5</v>
       </c>
-      <c r="E65" s="5">
+      <c r="I65" s="5">
         <v>0.2</v>
       </c>
+      <c r="L65">
+        <v>25.5</v>
+      </c>
+      <c r="M65">
+        <v>0.2</v>
+      </c>
+      <c r="O65">
+        <v>10</v>
+      </c>
+      <c r="P65">
+        <f>E76-E77</f>
+        <v>1.5</v>
+      </c>
+      <c r="Q65">
+        <f>D77</f>
+        <v>17</v>
+      </c>
+      <c r="R65">
+        <f>P65*Q65</f>
+        <v>25.5</v>
+      </c>
+      <c r="S65">
+        <f>LOG(AG2)</f>
+        <v>1.0374264979406236</v>
+      </c>
     </row>
-    <row r="66" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D66" s="6">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B66" s="26">
+        <v>45</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66">
         <v>37.5</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66">
+        <v>0.5</v>
+      </c>
+      <c r="H66" s="6">
+        <v>37.5</v>
+      </c>
+      <c r="I66" s="6">
         <v>0.4</v>
       </c>
+      <c r="L66" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="O66">
+        <v>15</v>
+      </c>
+      <c r="P66">
+        <f>E72-E73</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q66">
+        <f>D72</f>
+        <v>19.5</v>
+      </c>
+      <c r="R66">
+        <f t="shared" ref="R66:R72" si="16">P66*Q66</f>
+        <v>21.450000000000003</v>
+      </c>
+      <c r="S66">
+        <f>LOG(AG3)</f>
+        <v>1.1958996524092338</v>
+      </c>
     </row>
-    <row r="67" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D67" s="5">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B67" s="26"/>
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67">
+        <v>37.5</v>
+      </c>
+      <c r="E67">
+        <v>0.4</v>
+      </c>
+      <c r="H67" s="5">
         <v>39</v>
       </c>
-      <c r="E67" s="5">
+      <c r="I67" s="5">
         <v>0.25</v>
       </c>
+      <c r="L67" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="O67">
+        <v>20</v>
+      </c>
+      <c r="P67">
+        <f>E68-E69</f>
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="Q67">
+        <f>D68</f>
+        <v>21.5</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="16"/>
+        <v>22.037499999999998</v>
+      </c>
+      <c r="S67">
+        <f>LOG(AG4)</f>
+        <v>1.3053513694466237</v>
+      </c>
     </row>
-    <row r="68" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D68" s="6">
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B68" s="26">
+        <v>20</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68">
         <v>21.5</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68">
+        <v>1.2</v>
+      </c>
+      <c r="H68" s="6">
+        <v>21.5</v>
+      </c>
+      <c r="I68" s="6">
         <v>1</v>
       </c>
+      <c r="L68" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="M68" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="O68">
+        <v>25</v>
+      </c>
+      <c r="P68">
+        <f>E64-E65</f>
+        <v>0.90000000000000013</v>
+      </c>
+      <c r="Q68">
+        <f>D65</f>
+        <v>24</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="16"/>
+        <v>21.6</v>
+      </c>
+      <c r="S68">
+        <f>LOG(AG5)</f>
+        <v>1.403120521175818</v>
+      </c>
     </row>
-    <row r="69" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D69" s="5">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B69" s="26"/>
+      <c r="C69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69">
+        <v>21.5</v>
+      </c>
+      <c r="E69">
+        <f>AVERAGE(M24:M25)</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F69">
+        <f>M24 -M25</f>
+        <v>5.0000000000000017E-2</v>
+      </c>
+      <c r="H69" s="5">
         <v>31</v>
       </c>
-      <c r="E69" s="5">
+      <c r="I69" s="5">
         <v>0.15</v>
       </c>
+      <c r="L69" s="1">
+        <v>23</v>
+      </c>
+      <c r="M69" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="O69">
+        <v>30</v>
+      </c>
+      <c r="P69">
+        <f>E78-E79</f>
+        <v>0.72500000000000009</v>
+      </c>
+      <c r="Q69">
+        <f>D78</f>
+        <v>27</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="16"/>
+        <v>19.575000000000003</v>
+      </c>
+      <c r="S69">
+        <f>LOG(AG6)</f>
+        <v>1.481442628502305</v>
+      </c>
     </row>
-    <row r="70" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D70" s="6">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B70" s="26">
+        <v>40</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70">
+        <v>33.5</v>
+      </c>
+      <c r="E70">
+        <f>AVERAGE(Q21:Q22)</f>
+        <v>0.7</v>
+      </c>
+      <c r="F70">
+        <f>Q21-Q22</f>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="H70" s="6">
         <v>31</v>
       </c>
-      <c r="E70" s="6">
+      <c r="I70" s="6">
         <v>0.8</v>
       </c>
+      <c r="O70">
+        <v>35</v>
+      </c>
+      <c r="P70">
+        <f>E74-E75</f>
+        <v>0.5</v>
+      </c>
+      <c r="Q70">
+        <f>D74</f>
+        <v>30</v>
+      </c>
+      <c r="R70">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="S70">
+        <f>LOG(AG7)</f>
+        <v>1.5440680443502757</v>
+      </c>
     </row>
-    <row r="71" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D71" s="5">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B71" s="26"/>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71">
+        <v>33.5</v>
+      </c>
+      <c r="E71">
+        <f>AVERAGE(Q23:Q24)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="F71">
+        <f>Q23-Q24</f>
+        <v>0.2</v>
+      </c>
+      <c r="H71" s="5">
         <v>38.5</v>
       </c>
-      <c r="E71" s="5">
+      <c r="I71" s="5">
         <v>0.2</v>
       </c>
+      <c r="O71">
+        <v>40</v>
+      </c>
+      <c r="P71">
+        <f>E70-E71</f>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="Q71">
+        <f>D70</f>
+        <v>33.5</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="16"/>
+        <v>13.399999999999997</v>
+      </c>
+      <c r="S71">
+        <f>LOG(AG8)</f>
+        <v>1.6020599913279623</v>
+      </c>
     </row>
-    <row r="72" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D72" s="6">
+    <row r="72" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B72" s="26">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72">
         <v>19.5</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72">
         <v>1.35</v>
       </c>
+      <c r="H72" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="I72" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="L72">
+        <v>19.5</v>
+      </c>
+      <c r="M72">
+        <v>1.35</v>
+      </c>
+      <c r="O72">
+        <v>45</v>
+      </c>
+      <c r="P72">
+        <f>E66-E67</f>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="Q72">
+        <f>D66</f>
+        <v>37.5</v>
+      </c>
+      <c r="R72">
+        <f t="shared" si="16"/>
+        <v>3.7499999999999991</v>
+      </c>
+      <c r="S72">
+        <f>LOG(AG9)</f>
+        <v>1.6503075231319364</v>
+      </c>
     </row>
-    <row r="73" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D73" s="9">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B73" s="26"/>
+      <c r="C73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73">
+        <v>19.5</v>
+      </c>
+      <c r="E73">
+        <f>AVERAGE(E55:E56)</f>
+        <v>0.25</v>
+      </c>
+      <c r="F73">
+        <f>E55-E56</f>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="H73" s="9">
         <v>24.5</v>
       </c>
-      <c r="E73" s="9">
+      <c r="I73" s="9">
         <v>0.15</v>
       </c>
     </row>
-    <row r="74" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D74" s="6">
+    <row r="74" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B74" s="26">
+        <v>35</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74">
         <v>30</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74">
         <v>0.8</v>
       </c>
+      <c r="H74" s="6">
+        <v>30</v>
+      </c>
+      <c r="I74" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="L74">
+        <v>30</v>
+      </c>
+      <c r="M74">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="75" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D75" s="9">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B75" s="26"/>
+      <c r="C75" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75">
+        <f>AVERAGE(I55:I56)</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="F75">
+        <f>I55-I56</f>
+        <v>0.2</v>
+      </c>
+      <c r="H75" s="9">
         <v>35.5</v>
       </c>
-      <c r="E75" s="9">
+      <c r="I75" s="9">
         <v>0.2</v>
       </c>
     </row>
-    <row r="76" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D76" s="6">
+    <row r="76" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B76" s="26">
+        <v>10</v>
+      </c>
+      <c r="C76" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76">
         <v>17</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76">
         <v>1.65</v>
       </c>
+      <c r="H76" s="6">
+        <v>17</v>
+      </c>
+      <c r="I76" s="6">
+        <v>1.65</v>
+      </c>
+      <c r="L76">
+        <v>17</v>
+      </c>
+      <c r="M76">
+        <v>1.65</v>
+      </c>
+      <c r="O76">
+        <f>1/O65</f>
+        <v>0.1</v>
+      </c>
     </row>
-    <row r="77" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D77" s="9">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B77" s="26"/>
+      <c r="C77" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77">
+        <v>17</v>
+      </c>
+      <c r="E77">
+        <v>0.15</v>
+      </c>
+      <c r="H77" s="9">
         <v>21</v>
       </c>
-      <c r="E77" s="9">
+      <c r="I77" s="9">
         <v>0.15</v>
       </c>
+      <c r="L77">
+        <v>21</v>
+      </c>
+      <c r="M77">
+        <v>0.15</v>
+      </c>
+      <c r="O77">
+        <f t="shared" ref="O77:O84" si="17">1/O66</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
     </row>
-    <row r="78" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D78" s="6">
+    <row r="78" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B78" s="26">
+        <v>30</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78">
         <v>27</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E78">
         <v>0.9</v>
       </c>
+      <c r="H78" s="6">
+        <v>27</v>
+      </c>
+      <c r="I78" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="L78">
+        <v>27</v>
+      </c>
+      <c r="M78">
+        <v>0.9</v>
+      </c>
+      <c r="O78">
+        <f t="shared" si="17"/>
+        <v>0.05</v>
+      </c>
     </row>
-    <row r="79" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D79" s="9">
+    <row r="79" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B79" s="26"/>
+      <c r="C79" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79">
+        <v>27</v>
+      </c>
+      <c r="E79">
+        <f>AVERAGE(Q57:Q58)</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H79" s="9">
         <v>37.5</v>
       </c>
-      <c r="E79" s="9">
+      <c r="I79" s="9">
         <v>0.15</v>
       </c>
+      <c r="L79" s="1">
+        <v>28</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="O79">
+        <f t="shared" si="17"/>
+        <v>0.04</v>
+      </c>
     </row>
-    <row r="80" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.25">
       <c r="D80" t="s">
         <v>22</v>
       </c>
       <c r="E80" t="s">
         <v>21</v>
       </c>
+      <c r="O80">
+        <f t="shared" si="17"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="O81">
+        <f t="shared" si="17"/>
+        <v>2.8571428571428571E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="O82">
+        <f t="shared" si="17"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="O83">
+        <f t="shared" si="17"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="75">
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="AA35:AA36"/>
+    <mergeCell ref="AB35:AB36"/>
+    <mergeCell ref="AD35:AD36"/>
+    <mergeCell ref="AE35:AE36"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="V35:V36"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U35:U36"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="AA34:AB34"/>
+    <mergeCell ref="D57:F58"/>
+    <mergeCell ref="H57:J58"/>
+    <mergeCell ref="L59:N60"/>
+    <mergeCell ref="P59:R60"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="H28:J29"/>
+    <mergeCell ref="L26:N27"/>
+    <mergeCell ref="P25:R26"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="D28:F29"/>
+    <mergeCell ref="L34:N34"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
@@ -5368,55 +10936,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L35:L36"/>
-    <mergeCell ref="H28:J29"/>
-    <mergeCell ref="L26:N27"/>
-    <mergeCell ref="P25:R26"/>
-    <mergeCell ref="H34:J34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="M35:M36"/>
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="D28:F29"/>
-    <mergeCell ref="D57:F58"/>
-    <mergeCell ref="H57:J58"/>
-    <mergeCell ref="L59:N60"/>
-    <mergeCell ref="P59:R60"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="V35:V36"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U35:U36"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="X35:X36"/>
-    <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="AA34:AB34"/>
-    <mergeCell ref="AA35:AA36"/>
-    <mergeCell ref="AB35:AB36"/>
-    <mergeCell ref="AD35:AD36"/>
-    <mergeCell ref="AE35:AE36"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AD34:AE34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
